--- a/business_forms/038_farm_business_registration_form--business_forms.xlsx
+++ b/business_forms/038_farm_business_registration_form--business_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -960,7 +960,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C167"/>
+  <dimension ref="A1:C166"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -2115,12 +2115,12 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>orchard</t>
+          <t>fruit</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Orchard</t>
+          <t>Fruit</t>
         </is>
       </c>
     </row>
@@ -2132,12 +2132,12 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>fruit</t>
+          <t>vegetable</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Fruit</t>
+          <t>Vegetable</t>
         </is>
       </c>
     </row>
@@ -2149,12 +2149,12 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>vegetable</t>
+          <t>greenhouse</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Vegetable</t>
+          <t>Greenhouse</t>
         </is>
       </c>
     </row>
@@ -2166,12 +2166,12 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>greenhouse</t>
+          <t>farmers_market</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Greenhouse</t>
+          <t>Farmers Market</t>
         </is>
       </c>
     </row>
@@ -2183,12 +2183,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>farmers_market</t>
+          <t>farmers_coop</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Farmers_Market</t>
+          <t>Farmers Coop</t>
         </is>
       </c>
     </row>
@@ -2200,12 +2200,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>farmers_coop</t>
+          <t>farmers_assn</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Farmers_Coop</t>
+          <t>Farmers Assn</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>farmers_assn</t>
+          <t>farmers_mccoy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Farmers_Assn</t>
+          <t>Farmers McCoy</t>
         </is>
       </c>
     </row>
@@ -2234,12 +2234,12 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>farmers_mccoy</t>
+          <t>farmers_mkt</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Farmers_McCoy</t>
+          <t>Farmers Mkt</t>
         </is>
       </c>
     </row>
@@ -2251,12 +2251,12 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>farmers_mkt</t>
+          <t>farmers_mkt_2</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Farmers_Mkt</t>
+          <t>Farmers Mkt 2</t>
         </is>
       </c>
     </row>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>farmers_mkt_2</t>
+          <t>farmers_mkt_3</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_2</t>
+          <t>Farmers Mkt 3</t>
         </is>
       </c>
     </row>
@@ -2285,12 +2285,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>farmers_mkt_3</t>
+          <t>farmers_mkt_4</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_3</t>
+          <t>Farmers Mkt 4</t>
         </is>
       </c>
     </row>
@@ -2302,12 +2302,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>farmers_mkt_4</t>
+          <t>farmers_mkt_5</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_4</t>
+          <t>Farmers Mkt 5</t>
         </is>
       </c>
     </row>
@@ -2319,12 +2319,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>farmers_mkt_5</t>
+          <t>farmers_mkt_6</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_5</t>
+          <t>Farmers Mkt 6</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>farmers_mkt_6</t>
+          <t>farmers_mkt_7</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_6</t>
+          <t>Farmers Mkt 7</t>
         </is>
       </c>
     </row>
@@ -2353,12 +2353,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>farmers_mkt_7</t>
+          <t>farmers_mkt_8</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_7</t>
+          <t>Farmers Mkt 8</t>
         </is>
       </c>
     </row>
@@ -2370,12 +2370,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>farmers_mkt_8</t>
+          <t>farmers_mkt_9</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_8</t>
+          <t>Farmers Mkt 9</t>
         </is>
       </c>
     </row>
@@ -2387,12 +2387,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>farmers_mkt_9</t>
+          <t>farmers_mkt_10</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_9</t>
+          <t>Farmers Mkt 10</t>
         </is>
       </c>
     </row>
@@ -2404,12 +2404,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>farmers_mkt_10</t>
+          <t>farmers_mkt_11</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_10</t>
+          <t>Farmers Mkt 11</t>
         </is>
       </c>
     </row>
@@ -2421,12 +2421,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>farmers_mkt_11</t>
+          <t>farmers_mkt_12</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_11</t>
+          <t>Farmers Mkt 12</t>
         </is>
       </c>
     </row>
@@ -2438,12 +2438,12 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>farmers_mkt_12</t>
+          <t>farmers_mkt_13</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_12</t>
+          <t>Farmers Mkt 13</t>
         </is>
       </c>
     </row>
@@ -2455,12 +2455,12 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>farmers_mkt_13</t>
+          <t>farmers_mkt_14</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_13</t>
+          <t>Farmers Mkt 14</t>
         </is>
       </c>
     </row>
@@ -2472,12 +2472,12 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>farmers_mkt_14</t>
+          <t>farmers_mkt_15</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_14</t>
+          <t>Farmers Mkt 15</t>
         </is>
       </c>
     </row>
@@ -2489,12 +2489,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>farmers_mkt_15</t>
+          <t>farmers_mkt_16</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_15</t>
+          <t>Farmers Mkt 16</t>
         </is>
       </c>
     </row>
@@ -2506,12 +2506,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>farmers_mkt_16</t>
+          <t>farmers_mkt_17</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_16</t>
+          <t>Farmers Mkt 17</t>
         </is>
       </c>
     </row>
@@ -2523,12 +2523,12 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>farmers_mkt_17</t>
+          <t>farmers_mkt_18</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_17</t>
+          <t>Farmers Mkt 18</t>
         </is>
       </c>
     </row>
@@ -2540,12 +2540,12 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>farmers_mkt_18</t>
+          <t>farmers_mkt_19</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_18</t>
+          <t>Farmers Mkt 19</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>farmers_mkt_19</t>
+          <t>farmers_mkt_20</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_19</t>
+          <t>Farmers Mkt 20</t>
         </is>
       </c>
     </row>
@@ -2574,12 +2574,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>farmers_mkt_20</t>
+          <t>farmers_mkt_21</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_20</t>
+          <t>Farmers Mkt 21</t>
         </is>
       </c>
     </row>
@@ -2591,12 +2591,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>farmers_mkt_21</t>
+          <t>farmers_mkt_22</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_21</t>
+          <t>Farmers Mkt 22</t>
         </is>
       </c>
     </row>
@@ -2608,12 +2608,12 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>farmers_mkt_22</t>
+          <t>farmers_mkt_23</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_22</t>
+          <t>Farmers Mkt 23</t>
         </is>
       </c>
     </row>
@@ -2625,12 +2625,12 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>farmers_mkt_23</t>
+          <t>farmers_mkt_24</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_23</t>
+          <t>Farmers Mkt 24</t>
         </is>
       </c>
     </row>
@@ -2642,12 +2642,12 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>farmers_mkt_24</t>
+          <t>farmers_mkt_25</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_24</t>
+          <t>Farmers Mkt 25</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>farmers_mkt_25</t>
+          <t>farmers_mkt_26</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_25</t>
+          <t>Farmers Mkt 26</t>
         </is>
       </c>
     </row>
@@ -2676,12 +2676,12 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>farmers_mkt_26</t>
+          <t>farmers_mkt_27</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_26</t>
+          <t>Farmers Mkt 27</t>
         </is>
       </c>
     </row>
@@ -2693,12 +2693,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>farmers_mkt_27</t>
+          <t>farmers_mkt_28</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_27</t>
+          <t>Farmers Mkt 28</t>
         </is>
       </c>
     </row>
@@ -2710,12 +2710,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>farmers_mkt_28</t>
+          <t>farmers_mkt_29</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_28</t>
+          <t>Farmers Mkt 29</t>
         </is>
       </c>
     </row>
@@ -2727,12 +2727,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>farmers_mkt_29</t>
+          <t>farmers_mkt_30</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_29</t>
+          <t>Farmers Mkt 30</t>
         </is>
       </c>
     </row>
@@ -2744,12 +2744,12 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>farmers_mkt_30</t>
+          <t>farmers_mkt_31</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_30</t>
+          <t>Farmers Mkt 31</t>
         </is>
       </c>
     </row>
@@ -2761,12 +2761,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>farmers_mkt_31</t>
+          <t>farmers_mkt_32</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_31</t>
+          <t>Farmers Mkt 32</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>farmers_mkt_32</t>
+          <t>farmers_mkt_33</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_32</t>
+          <t>Farmers Mkt 33</t>
         </is>
       </c>
     </row>
@@ -2795,12 +2795,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>farmers_mkt_33</t>
+          <t>farmers_mkt_34</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_33</t>
+          <t>Farmers Mkt 34</t>
         </is>
       </c>
     </row>
@@ -2812,12 +2812,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>farmers_mkt_34</t>
+          <t>farmers_mkt_35</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_34</t>
+          <t>Farmers Mkt 35</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2829,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>farmers_mkt_35</t>
+          <t>farmers_mkt_36</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_35</t>
+          <t>Farmers Mkt 36</t>
         </is>
       </c>
     </row>
@@ -2846,12 +2846,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>farmers_mkt_36</t>
+          <t>farmers_mkt_37</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_36</t>
+          <t>Farmers Mkt 37</t>
         </is>
       </c>
     </row>
@@ -2863,12 +2863,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>farmers_mkt_37</t>
+          <t>farmers_mkt_38</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_37</t>
+          <t>Farmers Mkt 38</t>
         </is>
       </c>
     </row>
@@ -2880,12 +2880,12 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>farmers_mkt_38</t>
+          <t>farmers_mkt_39</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_38</t>
+          <t>Farmers Mkt 39</t>
         </is>
       </c>
     </row>
@@ -2897,12 +2897,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>farmers_mkt_39</t>
+          <t>farmers_mkt_40</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_39</t>
+          <t>Farmers Mkt 40</t>
         </is>
       </c>
     </row>
@@ -2914,12 +2914,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>farmers_mkt_40</t>
+          <t>farmers_mkt_41</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_40</t>
+          <t>Farmers Mkt 41</t>
         </is>
       </c>
     </row>
@@ -2931,12 +2931,12 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>farmers_mkt_41</t>
+          <t>farmers_mkt_42</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_41</t>
+          <t>Farmers Mkt 42</t>
         </is>
       </c>
     </row>
@@ -2948,12 +2948,12 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>farmers_mkt_42</t>
+          <t>farmers_mkt_43</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_42</t>
+          <t>Farmers Mkt 43</t>
         </is>
       </c>
     </row>
@@ -2965,12 +2965,12 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>farmers_mkt_43</t>
+          <t>farmers_mkt_44</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_43</t>
+          <t>Farmers Mkt 44</t>
         </is>
       </c>
     </row>
@@ -2982,12 +2982,12 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>farmers_mkt_44</t>
+          <t>farmers_mkt_45</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_44</t>
+          <t>Farmers Mkt 45</t>
         </is>
       </c>
     </row>
@@ -2999,12 +2999,12 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>farmers_mkt_45</t>
+          <t>farmers_mkt_46</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_45</t>
+          <t>Farmers Mkt 46</t>
         </is>
       </c>
     </row>
@@ -3016,12 +3016,12 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>farmers_mkt_46</t>
+          <t>farmers_mkt_47</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_46</t>
+          <t>Farmers Mkt 47</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>farmers_mkt_47</t>
+          <t>farmers_mkt_48</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_47</t>
+          <t>Farmers Mkt 48</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3050,12 @@
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>farmers_mkt_48</t>
+          <t>farmers_mkt_49</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_48</t>
+          <t>Farmers Mkt 49</t>
         </is>
       </c>
     </row>
@@ -3067,29 +3067,29 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>farmers_mkt_49</t>
+          <t>farmers_mkt_50</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_49</t>
+          <t>Farmers Mkt 50</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>farm_business_type_choices</t>
+          <t>farm_business_licenses_choices</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>farmers_mkt_50</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Farmers_Mkt_50</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3101,12 +3101,12 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3152,12 +3152,12 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -3169,29 +3169,29 @@
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>farm_business_licenses_choices</t>
+          <t>farm_business_certifications_choices</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>usda</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>USDA</t>
         </is>
       </c>
     </row>
@@ -3203,12 +3203,12 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>usda</t>
+          <t>nop</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>USDA</t>
+          <t>NOP</t>
         </is>
       </c>
     </row>
@@ -3220,12 +3220,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>nop</t>
+          <t>organic</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>NOP</t>
+          <t>Organic</t>
         </is>
       </c>
     </row>
@@ -3237,12 +3237,12 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>organic</t>
+          <t>certified</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Organic</t>
+          <t>Certified</t>
         </is>
       </c>
     </row>
@@ -3254,12 +3254,12 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>certified</t>
+          <t>non_certified</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Certified</t>
+          <t>Non Certified</t>
         </is>
       </c>
     </row>
@@ -3271,12 +3271,12 @@
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>non_certified</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Non Certified</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3288,12 +3288,12 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3305,12 +3305,12 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -3322,12 +3322,12 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3339,12 +3339,12 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -3356,29 +3356,29 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>farm_business_certifications_choices</t>
+          <t>farm_business_insurance_choices</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>insurance</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Insurance</t>
         </is>
       </c>
     </row>
@@ -3390,12 +3390,12 @@
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>insurance</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3407,12 +3407,12 @@
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -3424,12 +3424,12 @@
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -3441,12 +3441,12 @@
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3458,12 +3458,12 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -3475,29 +3475,29 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>farm_business_insurance_choices</t>
+          <t>farm_business_bankruptcy_choices</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>bankruptcy</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Bankruptcy</t>
         </is>
       </c>
     </row>
@@ -3509,12 +3509,12 @@
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>bankruptcy</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Bankruptcy</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3526,12 +3526,12 @@
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -3543,12 +3543,12 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3560,12 +3560,12 @@
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -3577,29 +3577,29 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>farm_business_bankruptcy_choices</t>
+          <t>farm_business_liability_choices</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>liability</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Liability</t>
         </is>
       </c>
     </row>
@@ -3611,12 +3611,12 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>liability</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Liability</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3628,12 +3628,12 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -3645,12 +3645,12 @@
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3662,12 +3662,12 @@
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -3679,29 +3679,29 @@
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Required</t>
+          <t>Optional</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>farm_business_liability_choices</t>
+          <t>farm_business_fines_choices</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>optional</t>
+          <t>fines</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Optional</t>
+          <t>Fines</t>
         </is>
       </c>
     </row>
@@ -3713,12 +3713,12 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>fines</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Fines</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -3730,12 +3730,12 @@
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>maybe</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Maybe</t>
         </is>
       </c>
     </row>
@@ -3747,12 +3747,12 @@
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>maybe</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Maybe</t>
+          <t>Pending</t>
         </is>
       </c>
     </row>
@@ -3764,12 +3764,12 @@
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>required</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Required</t>
         </is>
       </c>
     </row>
@@ -3781,27 +3781,10 @@
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>required</t>
+          <t>optional</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
-        <is>
-          <t>Required</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>farm_business_fines_choices</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
         <is>
           <t>Optional</t>
         </is>
